--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.01_Q20_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.01_Q20_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0006483281996189956</v>
+        <v>0.000246524633026482</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0006483281996189956</v>
+        <v>0.000246524633026482</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0006151424797304672</v>
+        <v>0.0002313544190044206</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0006151424797304672</v>
+        <v>0.0002313544190044206</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0005850240747753101</v>
+        <v>0.0002180743206809693</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0005850240747753101</v>
+        <v>0.0002180743206809693</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0005795400287813047</v>
+        <v>0.000215752988842354</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0005795400287813047</v>
+        <v>0.000215752988842354</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0006191686274360965</v>
+        <v>0.0002304310613166834</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0006191686274360965</v>
+        <v>0.0002304310613166834</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0007165720477219212</v>
+        <v>0.0002710666387359131</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007165720477219212</v>
+        <v>0.0002710666387359131</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0008916477544183834</v>
+        <v>0.0003403213028349242</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0008916477544183834</v>
+        <v>0.0003403213028349242</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.00113387625231446</v>
+        <v>0.0004351789784445794</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00113387625231446</v>
+        <v>0.0004351789784445794</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.001423509728613622</v>
+        <v>0.000547272935019308</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001423509728613622</v>
+        <v>0.000547272935019308</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.001735706282174953</v>
+        <v>0.0006663804343796163</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001735706282174953</v>
+        <v>0.0006663804343796163</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.002034519483305257</v>
+        <v>0.0007788401414125625</v>
       </c>
       <c r="C12" t="n">
-        <v>0.002034519483305257</v>
+        <v>0.0007788401414125625</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.002356389084475385</v>
+        <v>0.0008999647601629327</v>
       </c>
       <c r="C13" t="n">
-        <v>0.002356389084475385</v>
+        <v>0.0008999647601629327</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.002744995110400959</v>
+        <v>0.001047982643789473</v>
       </c>
       <c r="C14" t="n">
-        <v>0.002744995110400959</v>
+        <v>0.001047982643789473</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.003180204912106535</v>
+        <v>0.001215521981378217</v>
       </c>
       <c r="C15" t="n">
-        <v>0.003180204912106535</v>
+        <v>0.001215521981378217</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.003601700086982127</v>
+        <v>0.001378648979587422</v>
       </c>
       <c r="C16" t="n">
-        <v>0.003601700086982127</v>
+        <v>0.001378648979587422</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.003944501894773588</v>
+        <v>0.001511712220472617</v>
       </c>
       <c r="C17" t="n">
-        <v>0.003944501894773588</v>
+        <v>0.001511712220472617</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.004238115848385586</v>
+        <v>0.001625297989647843</v>
       </c>
       <c r="C18" t="n">
-        <v>0.004238115848385586</v>
+        <v>0.001625297989647843</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.004441206371331314</v>
+        <v>0.001703493076208077</v>
       </c>
       <c r="C19" t="n">
-        <v>0.004441206371331314</v>
+        <v>0.001703493076208077</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.004571464992537245</v>
+        <v>0.001752817300235755</v>
       </c>
       <c r="C20" t="n">
-        <v>0.004571464992537245</v>
+        <v>0.001752817300235755</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.00461734014664202</v>
+        <v>0.001769141387063109</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00461734014664202</v>
+        <v>0.001769141387063109</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.004634175111899401</v>
+        <v>0.001774027963172311</v>
       </c>
       <c r="C22" t="n">
-        <v>0.004634175111899401</v>
+        <v>0.001774027963172311</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.004561865919740732</v>
+        <v>0.00174501495626517</v>
       </c>
       <c r="C23" t="n">
-        <v>0.004561865919740732</v>
+        <v>0.00174501495626517</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.00447938904029273</v>
+        <v>0.001712541590213655</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00447938904029273</v>
+        <v>0.001712541590213655</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.004370799606653298</v>
+        <v>0.001670914044707855</v>
       </c>
       <c r="C25" t="n">
-        <v>0.004370799606653298</v>
+        <v>0.001670914044707855</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.004246147209927279</v>
+        <v>0.001623627637045615</v>
       </c>
       <c r="C26" t="n">
-        <v>0.004246147209927279</v>
+        <v>0.001623627637045615</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.004145614501690431</v>
+        <v>0.001585266206745006</v>
       </c>
       <c r="C27" t="n">
-        <v>0.004145614501690431</v>
+        <v>0.001585266206745006</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.00395466635595494</v>
+        <v>0.001513068169476178</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00395466635595494</v>
+        <v>0.001513068169476178</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.003841671139882423</v>
+        <v>0.001470165393730771</v>
       </c>
       <c r="C29" t="n">
-        <v>0.003841671139882423</v>
+        <v>0.001470165393730771</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.003786959577238938</v>
+        <v>0.001450056293550462</v>
       </c>
       <c r="C30" t="n">
-        <v>0.003786959577238938</v>
+        <v>0.001450056293550462</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.003710614161591006</v>
+        <v>0.001421159429695509</v>
       </c>
       <c r="C31" t="n">
-        <v>0.003710614161591006</v>
+        <v>0.001421159429695509</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
